--- a/game-stats/Week6_LOB_vs_K2.xlsx
+++ b/game-stats/Week6_LOB_vs_K2.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1294,6 +1294,45 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Michael Johnson</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WR/DL</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1851,16 +1890,16 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Mohammed Aqrabawi</t>
+          <t>Ahmad Jaffal</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>DL/WR</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -1890,16 +1929,16 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Jaffal</t>
+          <t>Ibrahim Ahmed</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -1929,16 +1968,16 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Ibrahim Ahmed</t>
+          <t>Yusuf Saleh</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>DB/WR</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -1968,16 +2007,16 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Yusuf Saleh</t>
+          <t>Aleem Abdulla</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>DB/WR</t>
+          <t>S/RB</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -2007,16 +2046,16 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aleem Abdulla</t>
+          <t>Jooma Abderazzaq</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>S/RB</t>
+          <t>OL/DL</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">

--- a/game-stats/Week6_LOB_vs_K2.xlsx
+++ b/game-stats/Week6_LOB_vs_K2.xlsx
@@ -522,20 +522,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,40 +562,70 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Pass Comp</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Pass Att</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Pass YDs</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Pass TDs</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>INTs</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Rush Att</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Rush YDs</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>INTs</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Def INTs</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>PBU</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -633,6 +669,24 @@
       <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -672,6 +726,24 @@
       <c r="K3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -711,6 +783,24 @@
       <c r="K4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -750,6 +840,24 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -789,19 +897,37 @@
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Gregory Hoard</t>
+          <t>Khaled Salah</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>WR/DL</t>
+          <t>WR/CB</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -826,21 +952,39 @@
         <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Khaled Salah</t>
+          <t>Othman Othman</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>WR/CB</t>
+          <t>WR/S</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -865,21 +1009,39 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Othman Othman</t>
+          <t>Abed Salah</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>OL/DL</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
@@ -904,21 +1066,39 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Abed Salah</t>
+          <t>Housam Abdallah</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>QB</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -943,21 +1123,39 @@
         <v>0</v>
       </c>
       <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Housam Abdallah</t>
+          <t>Ammar Zorub</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE/DL</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
@@ -982,21 +1180,39 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Ammar Zorub</t>
+          <t>Naseem Elmosa</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>TE/DL</t>
+          <t>OL/DL</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
@@ -1021,21 +1237,39 @@
         <v>0</v>
       </c>
       <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Naseem Elmosa</t>
+          <t>Ibrahim Kishta</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>OL/DL</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
@@ -1060,21 +1294,39 @@
         <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Ibrahim Kishta</t>
+          <t>Abdallah Qasem</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>WR/S</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -1099,21 +1351,39 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Abdallah Qasem</t>
+          <t>Gillz</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>WR/S</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
@@ -1138,21 +1408,39 @@
         <v>0</v>
       </c>
       <c r="K15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Gillz</t>
+          <t>Anthony Jordan</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>OC</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
@@ -1177,21 +1465,39 @@
         <v>0</v>
       </c>
       <c r="K16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>500</v>
+        <v>4</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Anthony Jordan</t>
+          <t>Yazen Abuzir</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>DL</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -1216,21 +1522,39 @@
         <v>0</v>
       </c>
       <c r="K17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Yazen Abuzir</t>
+          <t>Daniel Elmosa</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>DL</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -1255,21 +1579,39 @@
         <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Daniel Elmosa</t>
+          <t>Michael Johnson</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>WR/DL</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
@@ -1294,21 +1636,39 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Michael Johnson</t>
+          <t>Weezy</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>WR/DL</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
@@ -1333,6 +1693,24 @@
         <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1347,20 +1725,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1381,40 +1765,70 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Pass Comp</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Pass Att</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Pass YDs</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Pass TDs</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>INTs</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Rush Att</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Rush YDs</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>INTs</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Def INTs</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>PBU</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1458,6 +1872,24 @@
       <c r="K2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1497,6 +1929,24 @@
       <c r="K3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1534,6 +1984,24 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1575,6 +2043,24 @@
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1614,6 +2100,24 @@
       <c r="K6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -1653,6 +2157,24 @@
       <c r="K7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1692,6 +2214,24 @@
       <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1731,6 +2271,24 @@
       <c r="K9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1770,6 +2328,24 @@
       <c r="K10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1809,6 +2385,24 @@
       <c r="K11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1848,6 +2442,24 @@
       <c r="K12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1887,6 +2499,24 @@
       <c r="K13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1926,6 +2556,24 @@
       <c r="K14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1965,6 +2613,24 @@
       <c r="K15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2004,6 +2670,24 @@
       <c r="K16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2043,6 +2727,24 @@
       <c r="K17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="L17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2080,6 +2782,24 @@
         <v>0</v>
       </c>
       <c r="K18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week6_LOB_vs_K2.xlsx
+++ b/game-stats/Week6_LOB_vs_K2.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -539,7 +539,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
@@ -617,15 +617,20 @@
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -687,6 +692,9 @@
       <c r="Q2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -744,6 +752,9 @@
       <c r="Q3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -801,6 +812,9 @@
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -858,6 +872,9 @@
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -915,6 +932,9 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -972,6 +992,9 @@
       <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1029,6 +1052,9 @@
       <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1086,6 +1112,9 @@
       <c r="Q9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1143,6 +1172,9 @@
       <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1200,6 +1232,9 @@
       <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1257,6 +1292,9 @@
       <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1314,6 +1352,9 @@
       <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1371,6 +1412,9 @@
       <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1428,6 +1472,9 @@
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1485,6 +1532,9 @@
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1542,6 +1592,9 @@
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1597,6 +1650,9 @@
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1656,6 +1712,9 @@
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1711,6 +1770,9 @@
         <v>0</v>
       </c>
       <c r="Q20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1725,7 +1787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1742,7 +1804,7 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
@@ -1820,15 +1882,20 @@
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
+          <t>Def TDs</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1890,6 +1957,9 @@
       <c r="Q2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1947,6 +2017,9 @@
       <c r="Q3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2002,6 +2075,9 @@
         <v>0</v>
       </c>
       <c r="Q4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2061,6 +2137,9 @@
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2118,6 +2197,9 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2175,6 +2257,9 @@
       <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2232,6 +2317,9 @@
       <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -2289,6 +2377,9 @@
       <c r="Q9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -2346,6 +2437,9 @@
       <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -2403,6 +2497,9 @@
       <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -2460,6 +2557,9 @@
       <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -2517,6 +2617,9 @@
       <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -2574,6 +2677,9 @@
       <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -2631,6 +2737,9 @@
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2688,6 +2797,9 @@
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2745,6 +2857,9 @@
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="R17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2800,6 +2915,9 @@
         <v>0</v>
       </c>
       <c r="Q18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week6_LOB_vs_K2.xlsx
+++ b/game-stats/Week6_LOB_vs_K2.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
@@ -597,40 +597,45 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
+          <t>Rush TD</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Def TDs</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -695,6 +700,9 @@
       <c r="R2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -755,6 +763,9 @@
       <c r="R3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -815,6 +826,9 @@
       <c r="R4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -875,6 +889,9 @@
       <c r="R5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -935,6 +952,9 @@
       <c r="R6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -995,6 +1015,9 @@
       <c r="R7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -1055,6 +1078,9 @@
       <c r="R8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -1115,6 +1141,9 @@
       <c r="R9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1175,6 +1204,9 @@
       <c r="R10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1235,6 +1267,9 @@
       <c r="R11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1295,6 +1330,9 @@
       <c r="R12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -1355,6 +1393,9 @@
       <c r="R13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1415,6 +1456,9 @@
       <c r="R14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1475,6 +1519,9 @@
       <c r="R15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -1535,6 +1582,9 @@
       <c r="R16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1595,6 +1645,9 @@
       <c r="R17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1653,6 +1706,9 @@
         <v>0</v>
       </c>
       <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1715,6 +1771,9 @@
       <c r="R19" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1773,6 +1832,9 @@
         <v>0</v>
       </c>
       <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1787,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1800,7 +1862,7 @@
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
@@ -1862,40 +1924,45 @@
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
+          <t>Rush TD</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
           <t>REC</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Rec YDs</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>TDs</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Def INTs</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Def TDs</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>PBU</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Sacks</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Flag Pulls</t>
         </is>
@@ -1960,6 +2027,9 @@
       <c r="R2" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -2020,6 +2090,9 @@
       <c r="R3" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2078,6 +2151,9 @@
         <v>0</v>
       </c>
       <c r="R4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2140,6 +2216,9 @@
       <c r="R5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2200,6 +2279,9 @@
       <c r="R6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2260,6 +2342,9 @@
       <c r="R7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2320,6 +2405,9 @@
       <c r="R8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -2380,6 +2468,9 @@
       <c r="R9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -2440,6 +2531,9 @@
       <c r="R10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -2500,6 +2594,9 @@
       <c r="R11" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -2560,6 +2657,9 @@
       <c r="R12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -2620,6 +2720,9 @@
       <c r="R13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -2680,6 +2783,9 @@
       <c r="R14" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -2740,6 +2846,9 @@
       <c r="R15" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -2800,6 +2909,9 @@
       <c r="R16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -2860,6 +2972,9 @@
       <c r="R17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="S17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -2918,6 +3033,9 @@
         <v>0</v>
       </c>
       <c r="R18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/game-stats/Week6_LOB_vs_K2.xlsx
+++ b/game-stats/Week6_LOB_vs_K2.xlsx
@@ -1849,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3039,6 +3039,69 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Terryon Taylor</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/game-stats/Week6_LOB_vs_K2.xlsx
+++ b/game-stats/Week6_LOB_vs_K2.xlsx
@@ -61,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -77,11 +77,17 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -96,6 +102,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1437,7 +1447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="6" customWidth="1" style="7" min="1" max="1"/>
@@ -2745,7 +2755,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="7"/>
+    <row r="21" ht="15.75" customHeight="1" s="7">
+      <c r="A21" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Charles II</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="22" ht="15.75" customHeight="1" s="7"/>
     <row r="23" ht="15.75" customHeight="1" s="7"/>
     <row r="24" ht="15.75" customHeight="1" s="7"/>
@@ -4778,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0</v>
